--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="117">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,117 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Brazilian Serie A</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
+    <t>Finnish Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Romanian Liga I</t>
+  </si>
+  <si>
+    <t>Irish Premier Division</t>
+  </si>
+  <si>
+    <t>Moroccan Botola Pro 1</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:10:00</t>
+  </si>
+  <si>
+    <t>14:45:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>SE Palmeiras</t>
+  </si>
+  <si>
+    <t>Fortaleza FC</t>
+  </si>
+  <si>
+    <t>Qatar SC</t>
+  </si>
+  <si>
+    <t>SJK</t>
+  </si>
+  <si>
+    <t>FC Hunedoara</t>
+  </si>
+  <si>
+    <t>Al-Sadd</t>
+  </si>
+  <si>
+    <t>ACS Sepsi OSK</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Moghreb Tetouan</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Millonarios</t>
+  </si>
+  <si>
+    <t>Al Rayyan</t>
+  </si>
+  <si>
+    <t>Lahti</t>
+  </si>
+  <si>
+    <t>FC Voluntari</t>
+  </si>
+  <si>
+    <t>Al Arabi (QAT)</t>
+  </si>
+  <si>
+    <t>Dinamo Bucharest</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
+    <t>2026-10-07 02:01:18</t>
   </si>
 </sst>
 </file>
@@ -585,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +939,2426 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2">
+        <v>1.51</v>
+      </c>
+      <c r="G2">
+        <v>1.55</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
+      <c r="I2">
+        <v>8.6</v>
+      </c>
+      <c r="J2">
+        <v>4.3</v>
+      </c>
+      <c r="K2">
+        <v>4.8</v>
+      </c>
+      <c r="L2">
+        <v>1.35</v>
+      </c>
+      <c r="M2">
+        <v>1.04</v>
+      </c>
+      <c r="N2">
+        <v>3.7</v>
+      </c>
+      <c r="O2">
+        <v>1.3</v>
+      </c>
+      <c r="P2">
+        <v>1.89</v>
+      </c>
+      <c r="Q2">
+        <v>1.9</v>
+      </c>
+      <c r="R2">
+        <v>1.33</v>
+      </c>
+      <c r="S2">
+        <v>3.05</v>
+      </c>
+      <c r="T2">
+        <v>1.95</v>
+      </c>
+      <c r="U2">
+        <v>1.77</v>
+      </c>
+      <c r="V2">
+        <v>1.14</v>
+      </c>
+      <c r="W2">
+        <v>2.78</v>
+      </c>
+      <c r="X2">
+        <v>65</v>
+      </c>
+      <c r="Y2">
+        <v>28</v>
+      </c>
+      <c r="Z2">
+        <v>90</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC2">
+        <v>12</v>
+      </c>
+      <c r="AD2">
+        <v>34</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>10</v>
+      </c>
+      <c r="AG2">
+        <v>12</v>
+      </c>
+      <c r="AH2">
+        <v>30</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>17</v>
+      </c>
+      <c r="AK2">
+        <v>21</v>
+      </c>
+      <c r="AL2">
+        <v>50</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>10</v>
+      </c>
+      <c r="AQ2">
+        <v>3.25</v>
+      </c>
+      <c r="AR2">
+        <v>3.55</v>
+      </c>
+      <c r="AS2">
+        <v>3.7</v>
+      </c>
+      <c r="AT2">
+        <v>6.8</v>
+      </c>
+      <c r="AU2">
+        <v>7.8</v>
+      </c>
+      <c r="AV2">
+        <v>3.3</v>
+      </c>
+      <c r="AW2">
+        <v>3.7</v>
+      </c>
+      <c r="AX2">
+        <v>7</v>
+      </c>
+      <c r="AY2">
+        <v>7.8</v>
+      </c>
+      <c r="AZ2">
+        <v>3.3</v>
+      </c>
+      <c r="BA2">
+        <v>3.7</v>
+      </c>
+      <c r="BB2">
+        <v>10.5</v>
+      </c>
+      <c r="BC2">
+        <v>12.5</v>
+      </c>
+      <c r="BD2">
+        <v>3.45</v>
+      </c>
+      <c r="BE2">
+        <v>3.7</v>
+      </c>
+      <c r="BF2">
+        <v>6.2</v>
+      </c>
+      <c r="BG2">
+        <v>3.7</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.49</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>2.42</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>2.44</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>3.25</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>2.14</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>2.44</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>6.8</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>2.44</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>2.44</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>2.44</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3">
+        <v>1.58</v>
+      </c>
+      <c r="G3">
+        <v>1.62</v>
+      </c>
+      <c r="H3">
+        <v>5.8</v>
+      </c>
+      <c r="I3">
+        <v>6.6</v>
+      </c>
+      <c r="J3">
+        <v>4.5</v>
+      </c>
+      <c r="K3">
+        <v>4.7</v>
+      </c>
+      <c r="L3">
+        <v>1.32</v>
+      </c>
+      <c r="M3">
+        <v>1.02</v>
+      </c>
+      <c r="N3">
+        <v>4.7</v>
+      </c>
+      <c r="O3">
+        <v>1.21</v>
+      </c>
+      <c r="P3">
+        <v>2.32</v>
+      </c>
+      <c r="Q3">
+        <v>1.7</v>
+      </c>
+      <c r="R3">
+        <v>1.52</v>
+      </c>
+      <c r="S3">
+        <v>2.72</v>
+      </c>
+      <c r="T3">
+        <v>1.79</v>
+      </c>
+      <c r="U3">
+        <v>2.06</v>
+      </c>
+      <c r="V3">
+        <v>1.18</v>
+      </c>
+      <c r="W3">
+        <v>2.52</v>
+      </c>
+      <c r="X3">
+        <v>25</v>
+      </c>
+      <c r="Y3">
+        <v>28</v>
+      </c>
+      <c r="Z3">
+        <v>70</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>11.5</v>
+      </c>
+      <c r="AC3">
+        <v>11.5</v>
+      </c>
+      <c r="AD3">
+        <v>28</v>
+      </c>
+      <c r="AE3">
+        <v>100</v>
+      </c>
+      <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
+        <v>11.5</v>
+      </c>
+      <c r="AH3">
+        <v>25</v>
+      </c>
+      <c r="AI3">
+        <v>90</v>
+      </c>
+      <c r="AJ3">
+        <v>18</v>
+      </c>
+      <c r="AK3">
+        <v>19.5</v>
+      </c>
+      <c r="AL3">
+        <v>38</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO3">
+        <v>100</v>
+      </c>
+      <c r="AP3">
+        <v>15</v>
+      </c>
+      <c r="AQ3">
+        <v>17</v>
+      </c>
+      <c r="AR3">
+        <v>30</v>
+      </c>
+      <c r="AS3">
+        <v>5.2</v>
+      </c>
+      <c r="AT3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV3">
+        <v>17.5</v>
+      </c>
+      <c r="AW3">
+        <v>4.9</v>
+      </c>
+      <c r="AX3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY3">
+        <v>8.6</v>
+      </c>
+      <c r="AZ3">
+        <v>16</v>
+      </c>
+      <c r="BA3">
+        <v>5</v>
+      </c>
+      <c r="BB3">
+        <v>12</v>
+      </c>
+      <c r="BC3">
+        <v>12.5</v>
+      </c>
+      <c r="BD3">
+        <v>24</v>
+      </c>
+      <c r="BE3">
+        <v>5.2</v>
+      </c>
+      <c r="BF3">
+        <v>6</v>
+      </c>
+      <c r="BG3">
+        <v>4.9</v>
+      </c>
+      <c r="BH3">
+        <v>4.9</v>
+      </c>
+      <c r="BI3">
+        <v>3.1</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>2.3</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.66</v>
+      </c>
+      <c r="BN3">
+        <v>5.3</v>
+      </c>
+      <c r="BO3">
+        <v>3.3</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>2.3</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.66</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>2.3</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.66</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.66</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.66</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4">
+        <v>4.8</v>
+      </c>
+      <c r="G4">
+        <v>5.5</v>
+      </c>
+      <c r="H4">
+        <v>1.79</v>
+      </c>
+      <c r="I4">
+        <v>1.87</v>
+      </c>
+      <c r="J4">
+        <v>3.75</v>
+      </c>
+      <c r="K4">
+        <v>3.95</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.08</v>
+      </c>
+      <c r="N4">
+        <v>3.35</v>
+      </c>
+      <c r="O4">
+        <v>1.39</v>
+      </c>
+      <c r="P4">
+        <v>1.79</v>
+      </c>
+      <c r="Q4">
+        <v>2.1</v>
+      </c>
+      <c r="R4">
+        <v>1.3</v>
+      </c>
+      <c r="S4">
+        <v>3.95</v>
+      </c>
+      <c r="T4">
+        <v>2</v>
+      </c>
+      <c r="U4">
+        <v>1.89</v>
+      </c>
+      <c r="V4">
+        <v>2.14</v>
+      </c>
+      <c r="W4">
+        <v>1.22</v>
+      </c>
+      <c r="X4">
+        <v>13.5</v>
+      </c>
+      <c r="Y4">
+        <v>7.8</v>
+      </c>
+      <c r="Z4">
+        <v>10.5</v>
+      </c>
+      <c r="AA4">
+        <v>21</v>
+      </c>
+      <c r="AB4">
+        <v>15.5</v>
+      </c>
+      <c r="AC4">
+        <v>9</v>
+      </c>
+      <c r="AD4">
+        <v>11</v>
+      </c>
+      <c r="AE4">
+        <v>22</v>
+      </c>
+      <c r="AF4">
+        <v>48</v>
+      </c>
+      <c r="AG4">
+        <v>21</v>
+      </c>
+      <c r="AH4">
+        <v>24</v>
+      </c>
+      <c r="AI4">
+        <v>50</v>
+      </c>
+      <c r="AJ4">
+        <v>160</v>
+      </c>
+      <c r="AK4">
+        <v>100</v>
+      </c>
+      <c r="AL4">
+        <v>100</v>
+      </c>
+      <c r="AM4">
+        <v>170</v>
+      </c>
+      <c r="AN4">
+        <v>120</v>
+      </c>
+      <c r="AO4">
+        <v>15</v>
+      </c>
+      <c r="AP4">
+        <v>11.5</v>
+      </c>
+      <c r="AQ4">
+        <v>7</v>
+      </c>
+      <c r="AR4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS4">
+        <v>14.5</v>
+      </c>
+      <c r="AT4">
+        <v>13</v>
+      </c>
+      <c r="AU4">
+        <v>7.4</v>
+      </c>
+      <c r="AV4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW4">
+        <v>15.5</v>
+      </c>
+      <c r="AX4">
+        <v>29</v>
+      </c>
+      <c r="AY4">
+        <v>15</v>
+      </c>
+      <c r="AZ4">
+        <v>16.5</v>
+      </c>
+      <c r="BA4">
+        <v>30</v>
+      </c>
+      <c r="BB4">
+        <v>10</v>
+      </c>
+      <c r="BC4">
+        <v>9.4</v>
+      </c>
+      <c r="BD4">
+        <v>9.4</v>
+      </c>
+      <c r="BE4">
+        <v>10</v>
+      </c>
+      <c r="BF4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG4">
+        <v>12</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.04</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.04</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.04</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.04</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.04</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.04</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.04</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.04</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.04</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.04</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5">
+        <v>5.4</v>
+      </c>
+      <c r="G5">
+        <v>9.6</v>
+      </c>
+      <c r="H5">
+        <v>1.5</v>
+      </c>
+      <c r="I5">
+        <v>1.65</v>
+      </c>
+      <c r="J5">
+        <v>4.4</v>
+      </c>
+      <c r="K5">
+        <v>6.8</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>2.66</v>
+      </c>
+      <c r="Q5">
+        <v>1.43</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6">
+        <v>2.54</v>
+      </c>
+      <c r="G6">
+        <v>3.15</v>
+      </c>
+      <c r="H6">
+        <v>2.58</v>
+      </c>
+      <c r="I6">
+        <v>3.2</v>
+      </c>
+      <c r="J6">
+        <v>3.45</v>
+      </c>
+      <c r="K6">
+        <v>4.1</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>2.1</v>
+      </c>
+      <c r="Q6">
+        <v>1.62</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7">
+        <v>1.7</v>
+      </c>
+      <c r="G7">
+        <v>1.79</v>
+      </c>
+      <c r="H7">
+        <v>5.4</v>
+      </c>
+      <c r="I7">
+        <v>6.2</v>
+      </c>
+      <c r="J7">
+        <v>3.8</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.92</v>
+      </c>
+      <c r="Q7">
+        <v>1.94</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8">
+        <v>1.41</v>
+      </c>
+      <c r="G8">
+        <v>1.62</v>
+      </c>
+      <c r="H8">
+        <v>4.5</v>
+      </c>
+      <c r="I8">
+        <v>13</v>
+      </c>
+      <c r="J8">
+        <v>4.7</v>
+      </c>
+      <c r="K8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>3.3</v>
+      </c>
+      <c r="Q8">
+        <v>1.21</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9">
+        <v>4.7</v>
+      </c>
+      <c r="G9">
+        <v>5.1</v>
+      </c>
+      <c r="H9">
+        <v>1.85</v>
+      </c>
+      <c r="I9">
+        <v>1.91</v>
+      </c>
+      <c r="J9">
+        <v>3.6</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.74</v>
+      </c>
+      <c r="Q9">
+        <v>1.84</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10">
+        <v>1.41</v>
+      </c>
+      <c r="G10">
+        <v>1.43</v>
+      </c>
+      <c r="H10">
+        <v>7.8</v>
+      </c>
+      <c r="I10">
+        <v>9.4</v>
+      </c>
+      <c r="J10">
+        <v>4.8</v>
+      </c>
+      <c r="K10">
+        <v>5.4</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>2.3</v>
+      </c>
+      <c r="Q10">
+        <v>1.66</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11">
+        <v>1.1</v>
+      </c>
+      <c r="G11">
+        <v>600</v>
+      </c>
+      <c r="H11">
+        <v>1.1</v>
+      </c>
+      <c r="I11">
+        <v>870</v>
+      </c>
+      <c r="J11">
+        <v>1.12</v>
+      </c>
+      <c r="K11">
+        <v>950</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.07</v>
+      </c>
+      <c r="Q11">
+        <v>1.01</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="133">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,12 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>South Korean K1 League</t>
+  </si>
+  <si>
+    <t>South Korean K2 League</t>
+  </si>
+  <si>
     <t>Qatari Stars League</t>
   </si>
   <si>
@@ -286,6 +292,12 @@
     <t>01:10:00</t>
   </si>
   <si>
+    <t>05:00:00</t>
+  </si>
+  <si>
+    <t>07:30:00</t>
+  </si>
+  <si>
     <t>14:45:00</t>
   </si>
   <si>
@@ -313,6 +325,24 @@
     <t>Fortaleza FC</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
+    <t>Suwon FC</t>
+  </si>
+  <si>
+    <t>Incheon Utd</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Cheongju FC</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
     <t>Qatar SC</t>
   </si>
   <si>
@@ -343,6 +373,24 @@
     <t>Millonarios</t>
   </si>
   <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
+    <t>Hwaseong FC</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Bucheon FC 1995</t>
+  </si>
+  <si>
+    <t>Seongnam FC</t>
+  </si>
+  <si>
+    <t>Seoul E-Land FC</t>
+  </si>
+  <si>
     <t>Al Rayyan</t>
   </si>
   <si>
@@ -364,7 +412,7 @@
     <t>FUS Rabat</t>
   </si>
   <si>
-    <t>2026-10-07 02:01:18</t>
+    <t>2026-10-07 04:13:12</t>
   </si>
 </sst>
 </file>
@@ -696,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -946,19 +994,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F2">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G2">
         <v>1.55</v>
@@ -967,220 +1015,220 @@
         <v>7</v>
       </c>
       <c r="I2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L2">
         <v>1.35</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
         <v>1.3</v>
       </c>
       <c r="P2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="T2">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="V2">
         <v>1.14</v>
       </c>
       <c r="W2">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="X2">
-        <v>65</v>
+        <v>16.5</v>
       </c>
       <c r="Y2">
+        <v>23</v>
+      </c>
+      <c r="Z2">
+        <v>75</v>
+      </c>
+      <c r="AA2">
+        <v>280</v>
+      </c>
+      <c r="AB2">
+        <v>8</v>
+      </c>
+      <c r="AC2">
+        <v>10.5</v>
+      </c>
+      <c r="AD2">
         <v>28</v>
       </c>
-      <c r="Z2">
-        <v>90</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC2">
+      <c r="AE2">
+        <v>140</v>
+      </c>
+      <c r="AF2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG2">
+        <v>10.5</v>
+      </c>
+      <c r="AH2">
+        <v>26</v>
+      </c>
+      <c r="AI2">
+        <v>120</v>
+      </c>
+      <c r="AJ2">
+        <v>14</v>
+      </c>
+      <c r="AK2">
+        <v>18</v>
+      </c>
+      <c r="AL2">
+        <v>42</v>
+      </c>
+      <c r="AM2">
+        <v>170</v>
+      </c>
+      <c r="AN2">
+        <v>8.4</v>
+      </c>
+      <c r="AO2">
+        <v>190</v>
+      </c>
+      <c r="AP2">
+        <v>14</v>
+      </c>
+      <c r="AQ2">
+        <v>19</v>
+      </c>
+      <c r="AR2">
+        <v>10.5</v>
+      </c>
+      <c r="AS2">
         <v>12</v>
       </c>
-      <c r="AD2">
-        <v>34</v>
-      </c>
-      <c r="AE2">
-        <v>1000</v>
-      </c>
-      <c r="AF2">
-        <v>10</v>
-      </c>
-      <c r="AG2">
+      <c r="AT2">
+        <v>7.2</v>
+      </c>
+      <c r="AU2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV2">
+        <v>20</v>
+      </c>
+      <c r="AW2">
+        <v>11.5</v>
+      </c>
+      <c r="AX2">
+        <v>8</v>
+      </c>
+      <c r="AY2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>21</v>
+      </c>
+      <c r="BA2">
+        <v>11</v>
+      </c>
+      <c r="BB2">
         <v>12</v>
       </c>
-      <c r="AH2">
-        <v>30</v>
-      </c>
-      <c r="AI2">
-        <v>1000</v>
-      </c>
-      <c r="AJ2">
-        <v>17</v>
-      </c>
-      <c r="AK2">
-        <v>21</v>
-      </c>
-      <c r="AL2">
-        <v>50</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>10</v>
-      </c>
-      <c r="AQ2">
-        <v>3.25</v>
-      </c>
-      <c r="AR2">
-        <v>3.55</v>
-      </c>
-      <c r="AS2">
-        <v>3.7</v>
-      </c>
-      <c r="AT2">
-        <v>6.8</v>
-      </c>
-      <c r="AU2">
-        <v>7.8</v>
-      </c>
-      <c r="AV2">
-        <v>3.3</v>
-      </c>
-      <c r="AW2">
-        <v>3.7</v>
-      </c>
-      <c r="AX2">
-        <v>7</v>
-      </c>
-      <c r="AY2">
-        <v>7.8</v>
-      </c>
-      <c r="AZ2">
-        <v>3.3</v>
-      </c>
-      <c r="BA2">
-        <v>3.7</v>
-      </c>
-      <c r="BB2">
-        <v>10.5</v>
-      </c>
       <c r="BC2">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BD2">
-        <v>3.45</v>
+        <v>9.6</v>
       </c>
       <c r="BE2">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="BF2">
+        <v>7.4</v>
+      </c>
+      <c r="BG2">
+        <v>11.5</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.48</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>2.4</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>2.4</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.57</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
         <v>6.2</v>
       </c>
-      <c r="BG2">
-        <v>3.7</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.49</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>2.42</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>2.44</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>3.25</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>2.14</v>
-      </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>6.8</v>
+        <v>2.16</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1188,16 +1236,16 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F3">
         <v>1.58</v>
@@ -1206,13 +1254,13 @@
         <v>1.62</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
         <v>6.6</v>
       </c>
       <c r="J3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K3">
         <v>4.7</v>
@@ -1221,151 +1269,151 @@
         <v>1.32</v>
       </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O3">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P3">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q3">
         <v>1.7</v>
       </c>
       <c r="R3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S3">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="T3">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U3">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
         <v>1.18</v>
       </c>
       <c r="W3">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X3">
+        <v>22</v>
+      </c>
+      <c r="Y3">
         <v>25</v>
-      </c>
-      <c r="Y3">
-        <v>28</v>
       </c>
       <c r="Z3">
         <v>70</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE3">
         <v>100</v>
       </c>
       <c r="AF3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI3">
         <v>90</v>
       </c>
       <c r="AJ3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK3">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN3">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AO3">
         <v>100</v>
       </c>
       <c r="AP3">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AQ3">
-        <v>17</v>
+        <v>6.6</v>
       </c>
       <c r="AR3">
         <v>30</v>
       </c>
       <c r="AS3">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU3">
+        <v>9.4</v>
+      </c>
+      <c r="AV3">
+        <v>6.6</v>
+      </c>
+      <c r="AW3">
         <v>8.199999999999999</v>
       </c>
-      <c r="AV3">
+      <c r="AX3">
+        <v>9.4</v>
+      </c>
+      <c r="AY3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3">
         <v>17.5</v>
       </c>
-      <c r="AW3">
-        <v>4.9</v>
-      </c>
-      <c r="AX3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY3">
-        <v>8.6</v>
-      </c>
-      <c r="AZ3">
-        <v>16</v>
-      </c>
       <c r="BA3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BB3">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BC3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BD3">
         <v>24</v>
       </c>
       <c r="BE3">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG3">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -1377,25 +1425,25 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BN3">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BT3">
         <v>1000</v>
@@ -1407,22 +1455,22 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="CB3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1430,22 +1478,22 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F4">
         <v>4.8</v>
       </c>
       <c r="G4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H4">
         <v>1.79</v>
@@ -1454,7 +1502,7 @@
         <v>1.87</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
         <v>3.95</v>
@@ -1472,7 +1520,7 @@
         <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1484,16 +1532,16 @@
         <v>3.95</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V4">
         <v>2.14</v>
       </c>
       <c r="W4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X4">
         <v>13.5</v>
@@ -1565,25 +1613,25 @@
         <v>13</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4">
         <v>15.5</v>
       </c>
       <c r="AX4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AY4">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA4">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="BB4">
         <v>10</v>
@@ -1664,7 +1712,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1672,241 +1720,241 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F5">
-        <v>5.4</v>
+        <v>2.32</v>
       </c>
       <c r="G5">
-        <v>9.6</v>
+        <v>2.48</v>
       </c>
       <c r="H5">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
-        <v>1.65</v>
+        <v>3.35</v>
       </c>
       <c r="J5">
+        <v>3.65</v>
+      </c>
+      <c r="K5">
+        <v>3.75</v>
+      </c>
+      <c r="L5">
+        <v>1.34</v>
+      </c>
+      <c r="M5">
+        <v>1.06</v>
+      </c>
+      <c r="N5">
+        <v>4.1</v>
+      </c>
+      <c r="O5">
+        <v>1.27</v>
+      </c>
+      <c r="P5">
+        <v>2.04</v>
+      </c>
+      <c r="Q5">
+        <v>1.78</v>
+      </c>
+      <c r="R5">
+        <v>1.42</v>
+      </c>
+      <c r="S5">
+        <v>2.94</v>
+      </c>
+      <c r="T5">
+        <v>1.66</v>
+      </c>
+      <c r="U5">
+        <v>2.26</v>
+      </c>
+      <c r="V5">
+        <v>1.43</v>
+      </c>
+      <c r="W5">
+        <v>1.67</v>
+      </c>
+      <c r="X5">
+        <v>950</v>
+      </c>
+      <c r="Y5">
+        <v>950</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>23</v>
+      </c>
+      <c r="AC5">
+        <v>11</v>
+      </c>
+      <c r="AD5">
+        <v>950</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>50</v>
+      </c>
+      <c r="AG5">
+        <v>22</v>
+      </c>
+      <c r="AH5">
+        <v>950</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>60</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>12</v>
+      </c>
+      <c r="AQ5">
+        <v>10</v>
+      </c>
+      <c r="AR5">
+        <v>1.51</v>
+      </c>
+      <c r="AS5">
+        <v>1.51</v>
+      </c>
+      <c r="AT5">
+        <v>8.6</v>
+      </c>
+      <c r="AU5">
+        <v>6.6</v>
+      </c>
+      <c r="AV5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW5">
+        <v>1.51</v>
+      </c>
+      <c r="AX5">
+        <v>11</v>
+      </c>
+      <c r="AY5">
+        <v>8.4</v>
+      </c>
+      <c r="AZ5">
+        <v>11.5</v>
+      </c>
+      <c r="BA5">
+        <v>1.51</v>
+      </c>
+      <c r="BB5">
+        <v>1.51</v>
+      </c>
+      <c r="BC5">
+        <v>1.51</v>
+      </c>
+      <c r="BD5">
+        <v>1.51</v>
+      </c>
+      <c r="BE5">
+        <v>1.51</v>
+      </c>
+      <c r="BF5">
+        <v>11.5</v>
+      </c>
+      <c r="BG5">
+        <v>1.51</v>
+      </c>
+      <c r="BH5">
         <v>4.4</v>
       </c>
-      <c r="K5">
-        <v>6.8</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>2.66</v>
-      </c>
-      <c r="Q5">
-        <v>1.43</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>0</v>
-      </c>
-      <c r="BC5">
-        <v>0</v>
-      </c>
-      <c r="BD5">
-        <v>0</v>
-      </c>
-      <c r="BE5">
-        <v>0</v>
-      </c>
-      <c r="BF5">
-        <v>0</v>
-      </c>
-      <c r="BG5">
-        <v>0</v>
-      </c>
-      <c r="BH5">
-        <v>0</v>
-      </c>
       <c r="BI5">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="CB5" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1914,276 +1962,276 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F6">
-        <v>2.54</v>
+        <v>2.04</v>
       </c>
       <c r="G6">
-        <v>3.15</v>
+        <v>2.24</v>
       </c>
       <c r="H6">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="I6">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q6">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="F7">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="G7">
-        <v>1.79</v>
+        <v>2.56</v>
       </c>
       <c r="H7">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="I7">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="J7">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2198,10 +2246,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="Q7">
-        <v>1.94</v>
+        <v>2.44</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2390,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2398,34 +2446,34 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F8">
-        <v>1.41</v>
+        <v>1.8</v>
       </c>
       <c r="G8">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="H8">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>5.6</v>
       </c>
       <c r="J8">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>3.9</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2440,10 +2488,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>3.3</v>
+        <v>1.73</v>
       </c>
       <c r="Q8">
-        <v>1.21</v>
+        <v>2.16</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2632,42 +2680,42 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F9">
-        <v>4.7</v>
+        <v>2.74</v>
       </c>
       <c r="G9">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="H9">
-        <v>1.85</v>
+        <v>2.64</v>
       </c>
       <c r="I9">
-        <v>1.91</v>
+        <v>3.05</v>
       </c>
       <c r="J9">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2682,10 +2730,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="Q9">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2874,42 +2922,42 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F10">
-        <v>1.41</v>
+        <v>2.94</v>
       </c>
       <c r="G10">
-        <v>1.43</v>
+        <v>3.35</v>
       </c>
       <c r="H10">
-        <v>7.8</v>
+        <v>2.3</v>
       </c>
       <c r="I10">
-        <v>9.4</v>
+        <v>2.56</v>
       </c>
       <c r="J10">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="K10">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2924,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="Q10">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3116,249 +3164,1701 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11">
+        <v>5.4</v>
+      </c>
+      <c r="G11">
+        <v>6.8</v>
+      </c>
+      <c r="H11">
+        <v>1.54</v>
+      </c>
+      <c r="I11">
+        <v>1.65</v>
+      </c>
+      <c r="J11">
+        <v>4.6</v>
+      </c>
+      <c r="K11">
+        <v>5.5</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>2.78</v>
+      </c>
+      <c r="Q11">
+        <v>1.45</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12">
+        <v>2.54</v>
+      </c>
+      <c r="G12">
+        <v>3.1</v>
+      </c>
+      <c r="H12">
+        <v>2.58</v>
+      </c>
+      <c r="I12">
+        <v>3.15</v>
+      </c>
+      <c r="J12">
+        <v>3.5</v>
+      </c>
+      <c r="K12">
+        <v>4</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>2.1</v>
+      </c>
+      <c r="Q12">
+        <v>1.62</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
         <v>86</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13">
+        <v>1.72</v>
+      </c>
+      <c r="G13">
+        <v>1.82</v>
+      </c>
+      <c r="H13">
+        <v>5.1</v>
+      </c>
+      <c r="I13">
+        <v>6.2</v>
+      </c>
+      <c r="J13">
+        <v>3.8</v>
+      </c>
+      <c r="K13">
+        <v>4</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.92</v>
+      </c>
+      <c r="Q13">
+        <v>1.94</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14">
+        <v>1.49</v>
+      </c>
+      <c r="G14">
+        <v>1.84</v>
+      </c>
+      <c r="H14">
+        <v>3.3</v>
+      </c>
+      <c r="I14">
+        <v>7.8</v>
+      </c>
+      <c r="J14">
+        <v>4.9</v>
+      </c>
+      <c r="K14">
+        <v>950</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>3.3</v>
+      </c>
+      <c r="Q14">
+        <v>1.21</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F15">
+        <v>4.7</v>
+      </c>
+      <c r="G15">
+        <v>5.1</v>
+      </c>
+      <c r="H15">
+        <v>1.86</v>
+      </c>
+      <c r="I15">
+        <v>1.91</v>
+      </c>
+      <c r="J15">
+        <v>3.55</v>
+      </c>
+      <c r="K15">
+        <v>3.8</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1.81</v>
+      </c>
+      <c r="Q15">
+        <v>2</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
         <v>87</v>
       </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16">
+        <v>1.41</v>
+      </c>
+      <c r="G16">
+        <v>1.43</v>
+      </c>
+      <c r="H16">
+        <v>7.8</v>
+      </c>
+      <c r="I16">
+        <v>9.4</v>
+      </c>
+      <c r="J16">
+        <v>4.9</v>
+      </c>
+      <c r="K16">
+        <v>5.4</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>2.3</v>
+      </c>
+      <c r="Q16">
+        <v>1.66</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" t="s">
         <v>115</v>
       </c>
-      <c r="F11">
+      <c r="E17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F17">
         <v>1.1</v>
       </c>
-      <c r="G11">
+      <c r="G17">
         <v>600</v>
       </c>
-      <c r="H11">
+      <c r="H17">
         <v>1.1</v>
       </c>
-      <c r="I11">
+      <c r="I17">
         <v>870</v>
       </c>
-      <c r="J11">
+      <c r="J17">
         <v>1.12</v>
       </c>
-      <c r="K11">
+      <c r="K17">
         <v>950</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
         <v>1.07</v>
       </c>
-      <c r="Q11">
+      <c r="Q17">
         <v>1.01</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>0</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>0</v>
-      </c>
-      <c r="BC11">
-        <v>0</v>
-      </c>
-      <c r="BD11">
-        <v>0</v>
-      </c>
-      <c r="BE11">
-        <v>0</v>
-      </c>
-      <c r="BF11">
-        <v>0</v>
-      </c>
-      <c r="BG11">
-        <v>0</v>
-      </c>
-      <c r="BH11">
-        <v>0</v>
-      </c>
-      <c r="BI11">
-        <v>0</v>
-      </c>
-      <c r="BJ11">
-        <v>0</v>
-      </c>
-      <c r="BK11">
-        <v>0</v>
-      </c>
-      <c r="BL11">
-        <v>0</v>
-      </c>
-      <c r="BM11">
-        <v>0</v>
-      </c>
-      <c r="BN11">
-        <v>0</v>
-      </c>
-      <c r="BO11">
-        <v>0</v>
-      </c>
-      <c r="BP11">
-        <v>0</v>
-      </c>
-      <c r="BQ11">
-        <v>0</v>
-      </c>
-      <c r="BR11">
-        <v>0</v>
-      </c>
-      <c r="BS11">
-        <v>0</v>
-      </c>
-      <c r="BT11">
-        <v>0</v>
-      </c>
-      <c r="BU11">
-        <v>0</v>
-      </c>
-      <c r="BV11">
-        <v>0</v>
-      </c>
-      <c r="BW11">
-        <v>0</v>
-      </c>
-      <c r="BX11">
-        <v>0</v>
-      </c>
-      <c r="BY11">
-        <v>0</v>
-      </c>
-      <c r="BZ11">
-        <v>0</v>
-      </c>
-      <c r="CA11">
-        <v>0</v>
-      </c>
-      <c r="CB11" t="s">
-        <v>116</v>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
